--- a/example/i18n/langs/tw/other.xlsx
+++ b/example/i18n/langs/tw/other.xlsx
@@ -6,9 +6,8 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="other.ArgCaptureMode" r:id="rId3" sheetId="1"/>
-    <sheet name="other.drop" r:id="rId4" sheetId="2"/>
-    <sheet name="other.loot" r:id="rId5" sheetId="3"/>
+    <sheet name="other.drop" r:id="rId3" sheetId="1"/>
+    <sheet name="other.loot" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -69,8 +68,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -81,24 +79,24 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>t(comment)</t>
+          <t>t(name)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Snapshot</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>快照模式</t>
+          <t>测试掉落</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -110,15 +108,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dynamic</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>动态模式</t>
+          <t>剧情任务测试2</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>通告栏掉落染色模板1</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -187,95 +202,6 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>剧情任务测试2</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>通告栏掉落染色模板1</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="2" max="2" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>t(name)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>测试掉落</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>小宝箱</t>
         </is>
       </c>
